--- a/data/trans_orig/P42A-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P42A-Habitat-trans_orig.xlsx
@@ -673,12 +673,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>31995</t>
+          <t>32435</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>53753</t>
+          <t>55846</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -688,12 +688,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -708,12 +708,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>31995</t>
+          <t>32435</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>53753</t>
+          <t>55846</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -723,12 +723,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>28,03%</t>
         </is>
       </c>
     </row>
@@ -751,12 +751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22177</t>
+          <t>22586</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>42939</t>
+          <t>43075</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -786,12 +786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>22177</t>
+          <t>22586</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>42939</t>
+          <t>43075</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,62%</t>
         </is>
       </c>
     </row>
@@ -829,12 +829,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>39560</t>
+          <t>40222</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>64465</t>
+          <t>64725</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -864,12 +864,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>39560</t>
+          <t>40222</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>64465</t>
+          <t>64725</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>32,48%</t>
         </is>
       </c>
     </row>
@@ -907,12 +907,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>41517</t>
+          <t>40376</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>64878</t>
+          <t>64185</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -922,12 +922,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>32,21%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -942,12 +942,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>41517</t>
+          <t>40376</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>64878</t>
+          <t>64185</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -957,12 +957,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>32,21%</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>14187</t>
+          <t>14334</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>31720</t>
+          <t>30636</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1000,12 +1000,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1020,12 +1020,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>14187</t>
+          <t>14334</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>31720</t>
+          <t>30636</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1035,12 +1035,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,37%</t>
         </is>
       </c>
     </row>
@@ -1145,12 +1145,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>53730</t>
+          <t>53854</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>83574</t>
+          <t>84380</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1180,12 +1180,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>53730</t>
+          <t>53854</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>83574</t>
+          <t>84380</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,73%</t>
         </is>
       </c>
     </row>
@@ -1223,12 +1223,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>49775</t>
+          <t>49804</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>79045</t>
+          <t>80114</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>49775</t>
+          <t>49804</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>79045</t>
+          <t>80114</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>25,38%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>54039</t>
+          <t>55271</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>82485</t>
+          <t>83564</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>54039</t>
+          <t>55271</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>82485</t>
+          <t>83564</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>26,47%</t>
         </is>
       </c>
     </row>
@@ -1379,12 +1379,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>54500</t>
+          <t>53714</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>85555</t>
+          <t>82596</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1394,12 +1394,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1414,12 +1414,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>54500</t>
+          <t>53714</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>85555</t>
+          <t>82596</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>26,17%</t>
         </is>
       </c>
     </row>
@@ -1457,12 +1457,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>36260</t>
+          <t>36781</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>63047</t>
+          <t>63694</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1472,12 +1472,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1492,12 +1492,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>36260</t>
+          <t>36781</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>63047</t>
+          <t>63694</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1507,12 +1507,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>20,18%</t>
         </is>
       </c>
     </row>
@@ -1617,12 +1617,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>38307</t>
+          <t>36562</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>61943</t>
+          <t>61964</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1632,12 +1632,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>38307</t>
+          <t>36562</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>61943</t>
+          <t>61964</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1667,12 +1667,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>27,85%</t>
         </is>
       </c>
     </row>
@@ -1695,12 +1695,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>32458</t>
+          <t>31731</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>56911</t>
+          <t>56468</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>32458</t>
+          <t>31731</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>56911</t>
+          <t>56468</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1745,12 +1745,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,38%</t>
         </is>
       </c>
     </row>
@@ -1773,12 +1773,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>43386</t>
+          <t>42771</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>68436</t>
+          <t>67742</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>43386</t>
+          <t>42771</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>68436</t>
+          <t>67742</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>30,44%</t>
         </is>
       </c>
     </row>
@@ -1851,12 +1851,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>30935</t>
+          <t>31324</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>53733</t>
+          <t>54470</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1866,12 +1866,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>30935</t>
+          <t>31324</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>53733</t>
+          <t>54470</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>24,48%</t>
         </is>
       </c>
     </row>
@@ -1929,12 +1929,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>23417</t>
+          <t>22672</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>43949</t>
+          <t>43849</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1964,12 +1964,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>23417</t>
+          <t>22672</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>43949</t>
+          <t>43849</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1979,12 +1979,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,71%</t>
         </is>
       </c>
     </row>
@@ -2089,12 +2089,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>68244</t>
+          <t>68077</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>99367</t>
+          <t>98449</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2104,12 +2104,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>68244</t>
+          <t>68077</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>99367</t>
+          <t>98449</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>28,0%</t>
         </is>
       </c>
     </row>
@@ -2167,12 +2167,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>50523</t>
+          <t>51547</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>80241</t>
+          <t>81423</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2202,12 +2202,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>50523</t>
+          <t>51547</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>80241</t>
+          <t>81423</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2217,12 +2217,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>23,15%</t>
         </is>
       </c>
     </row>
@@ -2245,12 +2245,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>63332</t>
+          <t>62995</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>94196</t>
+          <t>93089</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>63332</t>
+          <t>62995</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>94196</t>
+          <t>93089</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>26,47%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>40540</t>
+          <t>40474</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>67331</t>
+          <t>68742</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>40540</t>
+          <t>40474</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>67331</t>
+          <t>68742</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,55%</t>
         </is>
       </c>
     </row>
@@ -2401,12 +2401,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>59409</t>
+          <t>59484</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>89120</t>
+          <t>88029</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -2416,12 +2416,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -2436,12 +2436,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>59409</t>
+          <t>59484</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>89120</t>
+          <t>88029</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,03%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>216668</t>
+          <t>217163</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>272275</t>
+          <t>272518</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>216668</t>
+          <t>217163</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>272275</t>
+          <t>272518</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>25,02%</t>
         </is>
       </c>
     </row>
@@ -2639,12 +2639,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>179079</t>
+          <t>179454</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>230349</t>
+          <t>229013</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -2654,12 +2654,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>179079</t>
+          <t>179454</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>230349</t>
+          <t>229013</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2689,12 +2689,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,03%</t>
         </is>
       </c>
     </row>
@@ -2717,12 +2717,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>226004</t>
+          <t>225706</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>282251</t>
+          <t>282422</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -2732,12 +2732,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -2752,12 +2752,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>226004</t>
+          <t>225706</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>282251</t>
+          <t>282422</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2767,12 +2767,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>25,93%</t>
         </is>
       </c>
     </row>
@@ -2795,12 +2795,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>188269</t>
+          <t>186685</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>239937</t>
+          <t>239848</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -2810,12 +2810,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -2830,12 +2830,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>188269</t>
+          <t>186685</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>239937</t>
+          <t>239848</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -2845,12 +2845,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>22,02%</t>
         </is>
       </c>
     </row>
@@ -2873,12 +2873,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>152302</t>
+          <t>149703</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>199774</t>
+          <t>197687</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -2888,12 +2888,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -2908,12 +2908,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>152302</t>
+          <t>149703</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>199774</t>
+          <t>197687</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2923,12 +2923,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,15%</t>
         </is>
       </c>
     </row>
@@ -3204,12 +3204,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>58019</t>
+          <t>57070</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>89785</t>
+          <t>90244</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3239,12 +3239,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>58019</t>
+          <t>57070</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>89785</t>
+          <t>90244</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,18%</t>
         </is>
       </c>
     </row>
@@ -3282,12 +3282,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>133498</t>
+          <t>132643</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>178214</t>
+          <t>178069</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>133498</t>
+          <t>132643</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>178214</t>
+          <t>178069</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>29,96%</t>
         </is>
       </c>
     </row>
@@ -3360,12 +3360,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>143385</t>
+          <t>141373</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>187157</t>
+          <t>187910</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3375,12 +3375,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>143385</t>
+          <t>141373</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>187157</t>
+          <t>187910</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3410,12 +3410,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>31,62%</t>
         </is>
       </c>
     </row>
@@ -3438,12 +3438,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>105458</t>
+          <t>102846</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>144050</t>
+          <t>143689</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>105458</t>
+          <t>102846</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>144050</t>
+          <t>143689</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3488,12 +3488,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,18%</t>
         </is>
       </c>
     </row>
@@ -3516,12 +3516,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>63850</t>
+          <t>63945</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>98474</t>
+          <t>96758</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>63850</t>
+          <t>63945</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>98474</t>
+          <t>96758</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,28%</t>
         </is>
       </c>
     </row>
@@ -3676,12 +3676,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>72713</t>
+          <t>73899</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>109470</t>
+          <t>110736</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3691,12 +3691,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3711,12 +3711,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>72713</t>
+          <t>73899</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>109470</t>
+          <t>110736</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,73%</t>
         </is>
       </c>
     </row>
@@ -3754,12 +3754,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>158236</t>
+          <t>156954</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>207670</t>
+          <t>205355</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3789,12 +3789,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>158236</t>
+          <t>156954</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>207670</t>
+          <t>205355</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3804,12 +3804,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,61%</t>
         </is>
       </c>
     </row>
@@ -3832,12 +3832,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>229387</t>
+          <t>228885</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>286051</t>
+          <t>284932</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>229387</t>
+          <t>228885</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>286051</t>
+          <t>284932</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>32,76%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>155688</t>
+          <t>158674</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>206906</t>
+          <t>210666</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>155688</t>
+          <t>158674</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>206906</t>
+          <t>210666</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>24,22%</t>
         </is>
       </c>
     </row>
@@ -3988,12 +3988,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>136953</t>
+          <t>136422</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>184766</t>
+          <t>184852</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4003,12 +4003,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4023,12 +4023,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>136953</t>
+          <t>136422</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>184766</t>
+          <t>184852</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4038,12 +4038,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,25%</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>40317</t>
+          <t>39643</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>68926</t>
+          <t>69373</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>40317</t>
+          <t>39643</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>68926</t>
+          <t>69373</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,97%</t>
         </is>
       </c>
     </row>
@@ -4226,12 +4226,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>130414</t>
+          <t>130026</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>175714</t>
+          <t>175821</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4261,12 +4261,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>130414</t>
+          <t>130026</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>175714</t>
+          <t>175821</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4276,12 +4276,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>25,28%</t>
         </is>
       </c>
     </row>
@@ -4304,12 +4304,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>170141</t>
+          <t>170995</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>220639</t>
+          <t>222157</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>170141</t>
+          <t>170995</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>220639</t>
+          <t>222157</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>31,94%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>137603</t>
+          <t>140020</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>186130</t>
+          <t>184583</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>137603</t>
+          <t>140020</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>186130</t>
+          <t>184583</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>26,54%</t>
         </is>
       </c>
     </row>
@@ -4460,12 +4460,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>113734</t>
+          <t>109742</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>156700</t>
+          <t>154299</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -4475,12 +4475,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -4495,12 +4495,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>113734</t>
+          <t>109742</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>156700</t>
+          <t>154299</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -4510,12 +4510,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>22,19%</t>
         </is>
       </c>
     </row>
@@ -4620,12 +4620,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>94094</t>
+          <t>94972</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>134973</t>
+          <t>134533</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>94094</t>
+          <t>94972</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>134973</t>
+          <t>134533</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,58%</t>
         </is>
       </c>
     </row>
@@ -4698,12 +4698,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>168683</t>
+          <t>168012</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>216622</t>
+          <t>216539</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -4713,12 +4713,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>168683</t>
+          <t>168012</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>216622</t>
+          <t>216539</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,47%</t>
         </is>
       </c>
     </row>
@@ -4776,12 +4776,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>268501</t>
+          <t>270146</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>328579</t>
+          <t>327201</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>35,47%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>268501</t>
+          <t>270146</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>328579</t>
+          <t>327201</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>35,47%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>165142</t>
+          <t>166546</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>215625</t>
+          <t>217261</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>165142</t>
+          <t>166546</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>215625</t>
+          <t>217261</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,55%</t>
         </is>
       </c>
     </row>
@@ -4932,12 +4932,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>110948</t>
+          <t>110554</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>156478</t>
+          <t>154081</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -4947,12 +4947,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -4967,12 +4967,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>110948</t>
+          <t>110554</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>156478</t>
+          <t>154081</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,7%</t>
         </is>
       </c>
     </row>
@@ -5092,12 +5092,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>296849</t>
+          <t>300342</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>367782</t>
+          <t>370388</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -5127,12 +5127,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>296849</t>
+          <t>300342</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>367782</t>
+          <t>370388</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>12,02%</t>
         </is>
       </c>
     </row>
@@ -5170,12 +5170,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>631373</t>
+          <t>628686</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>719081</t>
+          <t>723305</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -5185,12 +5185,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -5205,12 +5205,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>631373</t>
+          <t>628686</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>719081</t>
+          <t>723305</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,47%</t>
         </is>
       </c>
     </row>
@@ -5248,12 +5248,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>864750</t>
+          <t>867003</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>964897</t>
+          <t>971108</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -5263,12 +5263,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>31,31%</t>
+          <t>31,51%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>864750</t>
+          <t>867003</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>964897</t>
+          <t>971108</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>31,31%</t>
+          <t>31,51%</t>
         </is>
       </c>
     </row>
@@ -5326,12 +5326,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>608295</t>
+          <t>610983</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>705933</t>
+          <t>705323</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -5341,12 +5341,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -5361,12 +5361,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>608295</t>
+          <t>610983</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>705933</t>
+          <t>705323</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -5376,12 +5376,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>22,88%</t>
         </is>
       </c>
     </row>
@@ -5404,12 +5404,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>462863</t>
+          <t>462710</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>548642</t>
+          <t>543579</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -5419,12 +5419,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -5439,12 +5439,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>462863</t>
+          <t>462710</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>548642</t>
+          <t>543579</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -5454,12 +5454,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,64%</t>
         </is>
       </c>
     </row>
@@ -5735,12 +5735,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>39085</t>
+          <t>39264</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>67219</t>
+          <t>66732</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>39085</t>
+          <t>39264</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>67219</t>
+          <t>66732</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,06%</t>
         </is>
       </c>
     </row>
@@ -5813,12 +5813,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>131215</t>
+          <t>128341</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>170708</t>
+          <t>171809</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5828,12 +5828,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5848,12 +5848,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>131215</t>
+          <t>128341</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>170708</t>
+          <t>171809</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5863,12 +5863,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>31,05%</t>
         </is>
       </c>
     </row>
@@ -5891,12 +5891,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>170471</t>
+          <t>170762</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>215954</t>
+          <t>215844</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5906,12 +5906,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>39,02%</t>
+          <t>39,0%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5926,12 +5926,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>170471</t>
+          <t>170762</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>215954</t>
+          <t>215844</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>39,02%</t>
+          <t>39,0%</t>
         </is>
       </c>
     </row>
@@ -5969,12 +5969,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>59927</t>
+          <t>60215</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>90735</t>
+          <t>90893</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5984,12 +5984,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6004,12 +6004,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>59927</t>
+          <t>60215</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>90735</t>
+          <t>90893</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6019,12 +6019,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,42%</t>
         </is>
       </c>
     </row>
@@ -6047,12 +6047,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>69214</t>
+          <t>68433</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>102027</t>
+          <t>102542</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6062,12 +6062,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>69214</t>
+          <t>68433</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>102027</t>
+          <t>102542</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6097,12 +6097,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,53%</t>
         </is>
       </c>
     </row>
@@ -6207,12 +6207,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>42031</t>
+          <t>42806</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>73039</t>
+          <t>74833</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6222,12 +6222,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>42031</t>
+          <t>42806</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>73039</t>
+          <t>74833</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6257,12 +6257,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,21%</t>
         </is>
       </c>
     </row>
@@ -6285,12 +6285,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>217986</t>
+          <t>217866</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>276450</t>
+          <t>273663</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6300,12 +6300,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6320,12 +6320,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>217986</t>
+          <t>217866</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>276450</t>
+          <t>273663</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6335,12 +6335,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>30,02%</t>
         </is>
       </c>
     </row>
@@ -6363,12 +6363,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>295903</t>
+          <t>296581</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>354783</t>
+          <t>358331</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6378,12 +6378,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>32,53%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>38,92%</t>
+          <t>39,31%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6398,12 +6398,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>295903</t>
+          <t>296581</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>354783</t>
+          <t>358331</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6413,12 +6413,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>32,53%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>38,92%</t>
+          <t>39,31%</t>
         </is>
       </c>
     </row>
@@ -6441,12 +6441,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>145375</t>
+          <t>146997</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>195463</t>
+          <t>197592</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>145375</t>
+          <t>146997</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>195463</t>
+          <t>197592</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,68%</t>
         </is>
       </c>
     </row>
@@ -6519,12 +6519,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>95063</t>
+          <t>95194</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>137863</t>
+          <t>137071</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6534,12 +6534,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6554,12 +6554,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>95063</t>
+          <t>95194</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>137863</t>
+          <t>137071</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,04%</t>
         </is>
       </c>
     </row>
@@ -6679,12 +6679,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>52103</t>
+          <t>51836</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>84583</t>
+          <t>82544</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6694,12 +6694,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6714,12 +6714,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>52103</t>
+          <t>51836</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>84583</t>
+          <t>82544</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6729,12 +6729,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,24%</t>
         </is>
       </c>
     </row>
@@ -6757,12 +6757,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>98880</t>
+          <t>99586</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>139829</t>
+          <t>140690</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6792,12 +6792,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>98880</t>
+          <t>99586</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>139829</t>
+          <t>140690</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6807,12 +6807,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,85%</t>
         </is>
       </c>
     </row>
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>249769</t>
+          <t>247763</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>302109</t>
+          <t>299815</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>36,73%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>44,44%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>249769</t>
+          <t>247763</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>302109</t>
+          <t>299815</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>36,73%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>44,44%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>120407</t>
+          <t>119020</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>161676</t>
+          <t>161217</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>120407</t>
+          <t>119020</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>161676</t>
+          <t>161217</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>23,9%</t>
         </is>
       </c>
     </row>
@@ -6991,12 +6991,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>58212</t>
+          <t>59466</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>93059</t>
+          <t>92806</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7006,12 +7006,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7026,12 +7026,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>58212</t>
+          <t>59466</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>93059</t>
+          <t>92806</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7041,12 +7041,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,76%</t>
         </is>
       </c>
     </row>
@@ -7151,12 +7151,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>59931</t>
+          <t>59173</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>95442</t>
+          <t>96603</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7166,12 +7166,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7186,12 +7186,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>59931</t>
+          <t>59173</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>95442</t>
+          <t>96603</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7201,12 +7201,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,48%</t>
         </is>
       </c>
     </row>
@@ -7229,12 +7229,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>205868</t>
+          <t>208240</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>259400</t>
+          <t>261817</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7244,12 +7244,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>205868</t>
+          <t>208240</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>259400</t>
+          <t>261817</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7279,12 +7279,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>28,4%</t>
         </is>
       </c>
     </row>
@@ -7307,12 +7307,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282970</t>
+          <t>282701</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>343562</t>
+          <t>343100</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7322,12 +7322,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,67%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>37,22%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7342,12 +7342,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>282970</t>
+          <t>282701</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>343562</t>
+          <t>343100</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7357,12 +7357,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,67%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>37,22%</t>
         </is>
       </c>
     </row>
@@ -7385,12 +7385,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>156168</t>
+          <t>154977</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>205389</t>
+          <t>205148</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7420,12 +7420,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>156168</t>
+          <t>154977</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>205389</t>
+          <t>205148</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7435,12 +7435,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>22,25%</t>
         </is>
       </c>
     </row>
@@ -7463,12 +7463,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>101574</t>
+          <t>99770</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>143005</t>
+          <t>142822</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7478,12 +7478,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7498,12 +7498,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>101574</t>
+          <t>99770</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>143005</t>
+          <t>142822</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7513,12 +7513,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,49%</t>
         </is>
       </c>
     </row>
@@ -7623,12 +7623,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>221965</t>
+          <t>220412</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>284107</t>
+          <t>286588</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>221965</t>
+          <t>220412</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>284107</t>
+          <t>286588</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,36%</t>
         </is>
       </c>
     </row>
@@ -7701,12 +7701,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>699098</t>
+          <t>693107</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>800945</t>
+          <t>790271</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7716,12 +7716,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7736,12 +7736,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>699098</t>
+          <t>693107</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>800945</t>
+          <t>790271</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>25,81%</t>
         </is>
       </c>
     </row>
@@ -7779,12 +7779,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1056159</t>
+          <t>1051042</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1159639</t>
+          <t>1165721</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7794,12 +7794,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>38,08%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7814,12 +7814,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1056159</t>
+          <t>1051042</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1159639</t>
+          <t>1165721</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7829,12 +7829,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>38,08%</t>
         </is>
       </c>
     </row>
@@ -7857,12 +7857,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>521428</t>
+          <t>521348</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>607436</t>
+          <t>607285</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>521428</t>
+          <t>521348</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>607436</t>
+          <t>607285</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7935,12 +7935,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>354908</t>
+          <t>355994</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>434960</t>
+          <t>432145</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7950,12 +7950,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7970,12 +7970,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>354908</t>
+          <t>355994</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>434960</t>
+          <t>432145</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7985,12 +7985,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,12%</t>
         </is>
       </c>
     </row>
@@ -8261,32 +8261,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>47221</t>
+          <t>53264</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>38418</t>
+          <t>43090</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>57733</t>
+          <t>66475</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8296,32 +8296,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>47221</t>
+          <t>53264</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>38418</t>
+          <t>43090</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>57733</t>
+          <t>66475</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>15,04%</t>
         </is>
       </c>
     </row>
@@ -8339,32 +8339,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>138996</t>
+          <t>149246</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>125142</t>
+          <t>133950</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>155365</t>
+          <t>165806</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>33,77%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>37,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8374,32 +8374,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>138996</t>
+          <t>149246</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>125142</t>
+          <t>133950</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>155365</t>
+          <t>165806</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>33,77%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>37,52%</t>
         </is>
       </c>
     </row>
@@ -8417,32 +8417,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>117557</t>
+          <t>128722</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>103908</t>
+          <t>114588</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>131929</t>
+          <t>145486</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8452,32 +8452,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>117557</t>
+          <t>128722</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>103908</t>
+          <t>114588</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>131929</t>
+          <t>145486</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>32,92%</t>
         </is>
       </c>
     </row>
@@ -8495,32 +8495,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>62993</t>
+          <t>66384</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>52554</t>
+          <t>55781</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>75732</t>
+          <t>80545</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8530,32 +8530,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>62993</t>
+          <t>66384</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>52554</t>
+          <t>55781</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>75732</t>
+          <t>80545</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,23%</t>
         </is>
       </c>
     </row>
@@ -8573,32 +8573,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>43093</t>
+          <t>44270</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>32594</t>
+          <t>34768</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>53970</t>
+          <t>57097</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8608,32 +8608,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>43093</t>
+          <t>44270</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>32594</t>
+          <t>34768</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>53970</t>
+          <t>57097</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>12,92%</t>
         </is>
       </c>
     </row>
@@ -8651,17 +8651,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>409860</t>
+          <t>441886</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>409860</t>
+          <t>441886</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>409860</t>
+          <t>441886</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8686,17 +8686,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>409860</t>
+          <t>441886</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>409860</t>
+          <t>441886</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>409860</t>
+          <t>441886</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8733,32 +8733,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>70449</t>
+          <t>80925</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>58360</t>
+          <t>67566</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>84021</t>
+          <t>96311</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8768,32 +8768,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>70449</t>
+          <t>80925</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>58360</t>
+          <t>67566</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>84021</t>
+          <t>96311</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,93%</t>
         </is>
       </c>
     </row>
@@ -8811,32 +8811,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>172741</t>
+          <t>186747</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>156281</t>
+          <t>165679</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>192455</t>
+          <t>206975</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>29,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8846,32 +8846,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>172741</t>
+          <t>186747</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>156281</t>
+          <t>165679</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>192455</t>
+          <t>206975</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>29,93%</t>
         </is>
       </c>
     </row>
@@ -8889,32 +8889,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>184800</t>
+          <t>207219</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>166715</t>
+          <t>188015</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>201237</t>
+          <t>227515</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8924,32 +8924,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>184800</t>
+          <t>207219</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166715</t>
+          <t>188015</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>201237</t>
+          <t>227515</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>32,9%</t>
         </is>
       </c>
     </row>
@@ -8967,32 +8967,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>129267</t>
+          <t>144516</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>112843</t>
+          <t>124546</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>146956</t>
+          <t>162764</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9002,32 +9002,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>129267</t>
+          <t>144516</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>112843</t>
+          <t>124546</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>146956</t>
+          <t>162764</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,54%</t>
         </is>
       </c>
     </row>
@@ -9045,32 +9045,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>62994</t>
+          <t>72117</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>51250</t>
+          <t>59067</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>77469</t>
+          <t>89471</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9080,32 +9080,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>62994</t>
+          <t>72117</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>51250</t>
+          <t>59067</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>77469</t>
+          <t>89471</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,94%</t>
         </is>
       </c>
     </row>
@@ -9123,17 +9123,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>620250</t>
+          <t>691524</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>620250</t>
+          <t>691524</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>620250</t>
+          <t>691524</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9158,17 +9158,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>620250</t>
+          <t>691524</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>620250</t>
+          <t>691524</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>620250</t>
+          <t>691524</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9205,32 +9205,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>38643</t>
+          <t>43827</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>27774</t>
+          <t>34075</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>49936</t>
+          <t>54965</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9240,32 +9240,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>38643</t>
+          <t>43827</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>27774</t>
+          <t>34075</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>49936</t>
+          <t>54965</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,87%</t>
         </is>
       </c>
     </row>
@@ -9283,32 +9283,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>180700</t>
+          <t>170794</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>153132</t>
+          <t>153135</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>239020</t>
+          <t>189536</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>38,6%</t>
+          <t>33,77%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>51,06%</t>
+          <t>37,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9318,32 +9318,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>180700</t>
+          <t>170794</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>153132</t>
+          <t>153135</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>239020</t>
+          <t>189536</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>38,6%</t>
+          <t>33,77%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>51,06%</t>
+          <t>37,47%</t>
         </is>
       </c>
     </row>
@@ -9361,32 +9361,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>119858</t>
+          <t>137274</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>95737</t>
+          <t>119472</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>140299</t>
+          <t>155271</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>27,14%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9396,32 +9396,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>119858</t>
+          <t>137274</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>95737</t>
+          <t>119472</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>140299</t>
+          <t>155271</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>27,14%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>30,7%</t>
         </is>
       </c>
     </row>
@@ -9439,32 +9439,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>68736</t>
+          <t>82313</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>50698</t>
+          <t>68348</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>82626</t>
+          <t>98878</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9474,32 +9474,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>68736</t>
+          <t>82313</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>50698</t>
+          <t>68348</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>82626</t>
+          <t>98878</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>19,55%</t>
         </is>
       </c>
     </row>
@@ -9517,32 +9517,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>60150</t>
+          <t>71558</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>45830</t>
+          <t>57510</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>76124</t>
+          <t>87931</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9552,32 +9552,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>60150</t>
+          <t>71558</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>45830</t>
+          <t>57510</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>76124</t>
+          <t>87931</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>17,39%</t>
         </is>
       </c>
     </row>
@@ -9595,17 +9595,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>468088</t>
+          <t>505766</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>468088</t>
+          <t>505766</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>468088</t>
+          <t>505766</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9630,17 +9630,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>468088</t>
+          <t>505766</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>468088</t>
+          <t>505766</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>468088</t>
+          <t>505766</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9677,32 +9677,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>35981</t>
+          <t>42141</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>23942</t>
+          <t>32166</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>48261</t>
+          <t>54141</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9712,32 +9712,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>35981</t>
+          <t>42141</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>23942</t>
+          <t>32166</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>48261</t>
+          <t>54141</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>7,79%</t>
         </is>
       </c>
     </row>
@@ -9755,32 +9755,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>282365</t>
+          <t>228434</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>229160</t>
+          <t>209253</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>411029</t>
+          <t>249662</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>39,71%</t>
+          <t>32,88%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>57,8%</t>
+          <t>35,94%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9790,32 +9790,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>282365</t>
+          <t>228434</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>229160</t>
+          <t>209253</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>411029</t>
+          <t>249662</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>39,71%</t>
+          <t>32,88%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>57,8%</t>
+          <t>35,94%</t>
         </is>
       </c>
     </row>
@@ -9833,32 +9833,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>157247</t>
+          <t>168790</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>111773</t>
+          <t>150294</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>185305</t>
+          <t>189853</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9868,32 +9868,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>157247</t>
+          <t>168790</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>111773</t>
+          <t>150294</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>185305</t>
+          <t>189853</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>27,33%</t>
         </is>
       </c>
     </row>
@@ -9911,32 +9911,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>137374</t>
+          <t>151306</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>97575</t>
+          <t>132934</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>162015</t>
+          <t>172193</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9946,32 +9946,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>137374</t>
+          <t>151306</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>97575</t>
+          <t>132934</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>162015</t>
+          <t>172193</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>24,79%</t>
         </is>
       </c>
     </row>
@@ -9989,32 +9989,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>98117</t>
+          <t>104066</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>71181</t>
+          <t>87893</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>119760</t>
+          <t>120982</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10024,32 +10024,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>98117</t>
+          <t>104066</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>71181</t>
+          <t>87893</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>119760</t>
+          <t>120982</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>17,41%</t>
         </is>
       </c>
     </row>
@@ -10067,17 +10067,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>711084</t>
+          <t>694737</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>711084</t>
+          <t>694737</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>711084</t>
+          <t>694737</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -10102,17 +10102,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>711084</t>
+          <t>694737</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>711084</t>
+          <t>694737</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>711084</t>
+          <t>694737</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -10149,32 +10149,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>192294</t>
+          <t>220157</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>166333</t>
+          <t>196558</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>214861</t>
+          <t>246275</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10184,32 +10184,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>192294</t>
+          <t>220157</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>166333</t>
+          <t>196558</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>214861</t>
+          <t>246275</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>10,55%</t>
         </is>
       </c>
     </row>
@@ -10227,32 +10227,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>774802</t>
+          <t>735222</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>701678</t>
+          <t>698470</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>931017</t>
+          <t>773746</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>29,93%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>42,14%</t>
+          <t>33,15%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10262,32 +10262,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>774802</t>
+          <t>735222</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>701678</t>
+          <t>698470</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>931017</t>
+          <t>773746</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>29,93%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>42,14%</t>
+          <t>33,15%</t>
         </is>
       </c>
     </row>
@@ -10305,32 +10305,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>579463</t>
+          <t>642005</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>518490</t>
+          <t>608410</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>621769</t>
+          <t>679976</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10340,32 +10340,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>579463</t>
+          <t>642005</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>518490</t>
+          <t>608410</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>621769</t>
+          <t>679976</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>29,13%</t>
         </is>
       </c>
     </row>
@@ -10383,32 +10383,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>398370</t>
+          <t>444518</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>349986</t>
+          <t>411023</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>434617</t>
+          <t>477011</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>398370</t>
+          <t>444518</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>349986</t>
+          <t>411023</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>434617</t>
+          <t>477011</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>20,44%</t>
         </is>
       </c>
     </row>
@@ -10461,32 +10461,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>264354</t>
+          <t>292011</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>228091</t>
+          <t>264704</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>293426</t>
+          <t>319397</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>264354</t>
+          <t>292011</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>228091</t>
+          <t>264704</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>293426</t>
+          <t>319397</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,69%</t>
         </is>
       </c>
     </row>
@@ -10539,17 +10539,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>2209283</t>
+          <t>2333913</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2209283</t>
+          <t>2333913</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2209283</t>
+          <t>2333913</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -10574,17 +10574,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>2209283</t>
+          <t>2333913</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>2209283</t>
+          <t>2333913</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>2209283</t>
+          <t>2333913</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
